--- a/www/download/IND.value.m.mv.rpO2.xlsx
+++ b/www/download/IND.value.m.mv.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24.345</t>
+          <t>24345049.9967055</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.816</t>
+          <t>22816117.1229446</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.629</t>
+          <t>18628835.661079</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.563</t>
+          <t>20563005.4052722</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>32230360.3515103</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>42330297.5057876</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>45.965</t>
+          <t>45965371.3359364</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.991</t>
+          <t>41991425.7272939</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>38.429</t>
+          <t>38429196.3568261</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>39.799</t>
+          <t>39799487.713058</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>42.283</t>
+          <t>42283007.0698813</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>39.245</t>
+          <t>39244600.0083179</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>31.482</t>
+          <t>31482140.7719917</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>27.952</t>
+          <t>27952065.051838</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>21.974</t>
+          <t>21974208.2119378</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20.862</t>
+          <t>20862182.972245</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24.396</t>
+          <t>24395999.9879301</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.208</t>
+          <t>17207872.820972</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.565</t>
+          <t>18565141.784921</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28.698</t>
+          <t>28698312.3277024</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>43.215</t>
+          <t>43215078.6498642</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.133</t>
+          <t>50132811.0964357</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47.505</t>
+          <t>47504746.5851117</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>38.138</t>
+          <t>38137674.298625</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.735</t>
+          <t>33735006.5696923</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>37.072</t>
+          <t>37072328.9926539</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>41.548</t>
+          <t>41547646.803702</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>31.028</t>
+          <t>31027797.4591846</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>23.672</t>
+          <t>23672152.2117332</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16.332</t>
+          <t>16332161.9723705</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>22079940.0155612</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.768</t>
+          <t>20768129.4450979</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18049783.483807</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.666</t>
+          <t>18665944.1154791</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>25139835.5600457</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>38.473</t>
+          <t>38472858.0795316</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40.063</t>
+          <t>40063073.0248058</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>38.576</t>
+          <t>38576448.4628996</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>37.771</t>
+          <t>37770938.3493561</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>34.303</t>
+          <t>34303075.0113113</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>39.779</t>
+          <t>39778809.1094237</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>36.468</t>
+          <t>36468465.8472715</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>28.002</t>
+          <t>28002164.2261778</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>24.885</t>
+          <t>24884715.8377169</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19309754.0927181</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>53.689</t>
+          <t>53689355.4028271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.524</t>
+          <t>49523945.632795</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>49.977</t>
+          <t>49977297.1966779</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.585</t>
+          <t>43585374.482809</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47.356</t>
+          <t>47356144.5723706</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58659861.6303708</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70.278</t>
+          <t>70278132.1379299</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>71.842</t>
+          <t>71842385.5712752</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>67.435</t>
+          <t>67434619.2808063</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>64.224</t>
+          <t>64223838.8430573</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>62.085</t>
+          <t>62084790.7328699</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>62.507</t>
+          <t>62507152.1881645</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>46.723</t>
+          <t>46723368.7247178</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>40.86</t>
+          <t>40860310.4824855</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>29.857</t>
+          <t>29857420.1313034</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35769719.2152058</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>34149858.206346</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.435</t>
+          <t>30435339.4774962</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.901</t>
+          <t>31901075.7451843</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>47.747</t>
+          <t>47746925.3979546</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>55.604</t>
+          <t>55603633.2659498</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>66.444</t>
+          <t>66444459.4171784</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.266</t>
+          <t>65265555.3043075</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>58.864</t>
+          <t>58863904.7252599</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>56.479</t>
+          <t>56478603.0818665</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>45.474</t>
+          <t>45473678.8186553</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>40.056</t>
+          <t>40055851.3238119</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>33.868</t>
+          <t>33867627.5907663</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>30.525</t>
+          <t>30524637.9068749</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>24.441</t>
+          <t>24440603.8716024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20.488</t>
+          <t>20487575.3985841</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.081</t>
+          <t>20080816.3822383</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17.187</t>
+          <t>17186913.3502555</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.211</t>
+          <t>19211066.8557296</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23.556</t>
+          <t>23555581.7220116</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>33.861</t>
+          <t>33860583.0497679</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>41490399.5216473</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.294</t>
+          <t>32294172.4529232</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28.433</t>
+          <t>28432532.1613093</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28.187</t>
+          <t>28187082.3441157</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30.121</t>
+          <t>30121358.9323631</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28.17</t>
+          <t>28170125.1720395</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>22.092</t>
+          <t>22092469.5796864</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>19.219</t>
+          <t>19218651.6518647</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>14.724</t>
+          <t>14723986.5115061</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>206.077</t>
+          <t>206077372.98184</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>178.822</t>
+          <t>178821951.108355</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>148.31</t>
+          <t>148310190.855499</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>133.741</t>
+          <t>133741216.167303</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121309875.424526</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>133.901</t>
+          <t>133900784.86488</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>137.173</t>
+          <t>137172893.068879</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>135.583</t>
+          <t>135583151.098111</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>139.205</t>
+          <t>139204543.779663</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>133.451</t>
+          <t>133451407.069468</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>127.737</t>
+          <t>127737281.934043</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>111.508</t>
+          <t>111508098.637676</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>86.371</t>
+          <t>86370727.9103347</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>71.661</t>
+          <t>71661114.3822358</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>59.499</t>
+          <t>59498841.3553472</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38.581</t>
+          <t>38581291.2779284</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.794</t>
+          <t>46793717.0834969</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.448</t>
+          <t>28448327.6460763</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33.68</t>
+          <t>33679768.6098936</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>57.022</t>
+          <t>57021863.3416024</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>74.811</t>
+          <t>74810829.3551489</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>94.251</t>
+          <t>94251387.2393534</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>95.785</t>
+          <t>95785424.6484272</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>92.74</t>
+          <t>92740338.7957562</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>81.132</t>
+          <t>81131577.6780377</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>45.828</t>
+          <t>45827932.4993198</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>42.357</t>
+          <t>42356612.8294321</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>29.954</t>
+          <t>29953972.4325744</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>28620260.5489292</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>16.722</t>
+          <t>16722183.7791311</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21.694</t>
+          <t>21693723.9023144</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24350120.2415905</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.751</t>
+          <t>16750653.7173813</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21.765</t>
+          <t>21764787.7035625</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30.086</t>
+          <t>30086316.0003756</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>43.131</t>
+          <t>43130769.1967987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50.786</t>
+          <t>50785523.5248588</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>46.896</t>
+          <t>46895915.0680472</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>42.231</t>
+          <t>42231225.7813099</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>32.572</t>
+          <t>32571916.1814535</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>36.274</t>
+          <t>36274117.4013543</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>33.553</t>
+          <t>33553260.2888654</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>22.722</t>
+          <t>22722006.9568317</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>17.834</t>
+          <t>17833775.5895417</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11.898</t>
+          <t>11898006.54198</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16.785</t>
+          <t>16784996.4840027</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15919804.491716</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.387</t>
+          <t>15386925.7339348</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.116</t>
+          <t>17115818.5126136</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24.145</t>
+          <t>24144873.7262917</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>36.919</t>
+          <t>36918711.5196233</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>42.659</t>
+          <t>42659427.8934843</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>40.521</t>
+          <t>40521006.2257733</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>35.711</t>
+          <t>35710947.082778</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>31.191</t>
+          <t>31190632.1632419</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>33.568</t>
+          <t>33568000.7501839</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>34.785</t>
+          <t>34784812.0536835</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>25.086</t>
+          <t>25086108.7575295</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>19.738</t>
+          <t>19737758.815808</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>13.484</t>
+          <t>13484339.4170896</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.622</t>
+          <t>22622038.9972067</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23.252</t>
+          <t>23251631.2702554</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22250055.4568492</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25.965</t>
+          <t>25965335.9866709</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26.849</t>
+          <t>26849357.9119829</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>37.015</t>
+          <t>37014936.9330981</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>42439500.3472997</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.791</t>
+          <t>37790782.3318277</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.391</t>
+          <t>37391247.7424173</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36450180.5545525</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>36.664</t>
+          <t>36663662.5964189</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>32.175</t>
+          <t>32175315.9983117</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.487</t>
+          <t>24487408.3094678</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.328</t>
+          <t>20328431.4066453</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>15.654</t>
+          <t>15653916.5667559</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22.385</t>
+          <t>22384885.5247694</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22.195</t>
+          <t>22195476.7327419</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.811</t>
+          <t>20811234.6422738</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20.939</t>
+          <t>20938954.2658971</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>31.413</t>
+          <t>31413288.6448756</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>54.578</t>
+          <t>54578498.7314876</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>57.332</t>
+          <t>57331874.6329589</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>51.49</t>
+          <t>51490204.1642495</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46.742</t>
+          <t>46741685.8246405</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>45.681</t>
+          <t>45680994.2460716</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>52.094</t>
+          <t>52094328.423516</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>53.111</t>
+          <t>53110590.8736641</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>36.854</t>
+          <t>36853895.9054065</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>31.651</t>
+          <t>31651285.7695171</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>23.039</t>
+          <t>23039396.6589923</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>62.383</t>
+          <t>62382926.34779</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.191</t>
+          <t>53191429.3374179</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>68.568</t>
+          <t>68568050.6180928</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>71.286</t>
+          <t>71286124.8788295</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>34.891</t>
+          <t>34890938.3129995</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>106.839</t>
+          <t>106838730.448678</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>130.645</t>
+          <t>130644950.1631</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>110.855</t>
+          <t>110854907.657638</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>107.344</t>
+          <t>107344230.688112</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>57.975</t>
+          <t>57974948.1454646</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>42.617</t>
+          <t>42617465.019817</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>38.035</t>
+          <t>38034772.6774231</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>31.814</t>
+          <t>31814175.9529344</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>27.667</t>
+          <t>27666598.9270317</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>18.534</t>
+          <t>18533745.3828768</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18.474</t>
+          <t>18474207.9804859</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.151</t>
+          <t>17151111.6938425</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.222</t>
+          <t>13222343.2632171</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.285</t>
+          <t>14284673.946975</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20.519</t>
+          <t>20519264.570272</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30.646</t>
+          <t>30646052.5436308</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>32.485</t>
+          <t>32484525.7289396</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29.468</t>
+          <t>29468431.3167049</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29.118</t>
+          <t>29117601.338709</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.483</t>
+          <t>25482718.5509504</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>26009645.4105543</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>27.524</t>
+          <t>27524411.2827649</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>19.144</t>
+          <t>19143634.6957412</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.009</t>
+          <t>16009262.0147082</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>10.377</t>
+          <t>10376898.9929064</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19.361</t>
+          <t>19361025.6127317</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.398</t>
+          <t>18398164.9761177</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.668</t>
+          <t>15668278.1843814</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.593</t>
+          <t>17593209.8982743</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>26.105</t>
+          <t>26105468.8862874</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>42.663</t>
+          <t>42663045.4627172</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>43.571</t>
+          <t>43571027.9248191</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>40.966</t>
+          <t>40965622.9721585</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>38.385</t>
+          <t>38385024.9112494</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>34.923</t>
+          <t>34923041.6540054</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>41.557</t>
+          <t>41556704.6362902</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>40770102.2066099</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28710496.7519265</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>24.463</t>
+          <t>24463234.1388425</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>15.516</t>
+          <t>15515779.0617225</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24.366</t>
+          <t>24366343.1436675</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23.467</t>
+          <t>23467225.9574217</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18.087</t>
+          <t>18086588.8202124</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.824</t>
+          <t>17824461.9700404</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22.938</t>
+          <t>22938194.3080937</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>32.803</t>
+          <t>32802780.6710955</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>33.093</t>
+          <t>33092626.6073018</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29.753</t>
+          <t>29752998.5405482</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>30.167</t>
+          <t>30166730.7014562</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>28.667</t>
+          <t>28666919.5709629</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>31.736</t>
+          <t>31735852.7944344</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>31.615</t>
+          <t>31615080.4747056</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>24.505</t>
+          <t>24504587.7998742</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>20.657</t>
+          <t>20656914.2465683</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>16.718</t>
+          <t>16718340.1909588</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>24.213</t>
+          <t>24213083.6312182</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26.819</t>
+          <t>26818846.6700252</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.545</t>
+          <t>24545222.5481733</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27.744</t>
+          <t>27743835.9716936</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>32.122</t>
+          <t>32122047.3590423</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>64.487</t>
+          <t>64487354.0318259</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>61.618</t>
+          <t>61617721.6522045</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>48.689</t>
+          <t>48689257.1826631</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>44.512</t>
+          <t>44512452.1075389</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>41.908</t>
+          <t>41907851.1167415</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>47.797</t>
+          <t>47796752.7198437</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>57.313</t>
+          <t>57313226.7628874</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>41.465</t>
+          <t>41465057.4725629</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>35.527</t>
+          <t>35527359.568335</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>27.897</t>
+          <t>27897066.2839462</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>28.397</t>
+          <t>28397432.3315953</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.816</t>
+          <t>25816483.1346032</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.077</t>
+          <t>23077040.4298259</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27.219</t>
+          <t>27218753.7069868</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>33.386</t>
+          <t>33385734.303947</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>44.716</t>
+          <t>44716098.5515975</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>48.501</t>
+          <t>48500971.3263487</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>45.758</t>
+          <t>45758465.1136192</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>39.508</t>
+          <t>39508184.4720358</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>29.734</t>
+          <t>29734040.3821275</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>30.958</t>
+          <t>30958290.8709963</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>31369734.862686</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>23.949</t>
+          <t>23948743.1874707</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>16.891</t>
+          <t>16891232.3255575</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>12.479</t>
+          <t>12479316.4889711</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>62.871</t>
+          <t>62870935.2497324</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>60.768</t>
+          <t>60768083.3769531</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>57.575</t>
+          <t>57574655.0528275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>123.057</t>
+          <t>123057442.643337</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>94.028</t>
+          <t>94027762.1447606</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>110.512</t>
+          <t>110512206.78812</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>117.369</t>
+          <t>117368811.574126</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>110.24</t>
+          <t>110240317.895445</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>99.203</t>
+          <t>99202794.0412703</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>104.639</t>
+          <t>104638552.747351</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>96.994</t>
+          <t>96993607.2486685</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>73.973</t>
+          <t>73973033.5366403</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>58.279</t>
+          <t>58278536.4880753</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>48.544</t>
+          <t>48543835.4169962</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>36.085</t>
+          <t>36085134.5960664</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>194.67</t>
+          <t>194669924.591761</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>169.384</t>
+          <t>169384017.958643</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>151.184</t>
+          <t>151183690.587553</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>140.947</t>
+          <t>140946948.040728</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>153.12</t>
+          <t>153120316.688539</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>209.334</t>
+          <t>209334360.459221</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>238.946</t>
+          <t>238946187.356524</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>246.352</t>
+          <t>246351661.239077</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>236.567</t>
+          <t>236566744.233088</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>228.327</t>
+          <t>228327458.572113</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>216.318</t>
+          <t>216318101.767686</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>191.819</t>
+          <t>191818963.016798</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>151.475</t>
+          <t>151475071.02331</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>137.672</t>
+          <t>137672317.460277</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>130.597</t>
+          <t>130596580.992757</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>36.754</t>
+          <t>36754245.3922304</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32.416</t>
+          <t>32416104.4506263</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.582</t>
+          <t>26582241.8450408</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25409772.7306378</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>30.178</t>
+          <t>30178287.4659488</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>38.754</t>
+          <t>38753883.1369831</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>35.224</t>
+          <t>35223807.6090662</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>25.611</t>
+          <t>25611110.1675969</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>29.505</t>
+          <t>29505455.1654553</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>31.267</t>
+          <t>31266998.9116349</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>34.829</t>
+          <t>34829368.274968</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>30.945</t>
+          <t>30945487.5116825</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>23.754</t>
+          <t>23753761.8911347</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>27.085</t>
+          <t>27085398.1486651</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>26.768</t>
+          <t>26768346.1703559</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24.624</t>
+          <t>24624403.7435424</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24.808</t>
+          <t>24808420.9295762</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.766</t>
+          <t>21765610.9946653</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21.748</t>
+          <t>21748051.7914988</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.596</t>
+          <t>30595800.4294876</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>52.777</t>
+          <t>52777291.2412423</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>54.987</t>
+          <t>54986640.9741306</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>52.829</t>
+          <t>52828859.7188896</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>49.412</t>
+          <t>49412371.0127715</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>43.828</t>
+          <t>43828358.3780952</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>49.859</t>
+          <t>49858844.3592709</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>55.282</t>
+          <t>55281532.0898313</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>38.746</t>
+          <t>38746103.1411312</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>31.857</t>
+          <t>31857236.4491646</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>24.234</t>
+          <t>24234315.0694896</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18.944</t>
+          <t>18944123.6962221</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19080242.0788832</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.859</t>
+          <t>20859069.4033099</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21.505</t>
+          <t>21504949.3671704</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>25.502</t>
+          <t>25501718.7785851</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>39.409</t>
+          <t>39408544.870329</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>45.609</t>
+          <t>45608776.8197803</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>44.415</t>
+          <t>44414830.4588386</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>46.418</t>
+          <t>46418013.686807</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>46.488</t>
+          <t>46488111.2870855</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>55.883</t>
+          <t>55882629.5817224</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>59.804</t>
+          <t>59803750.3067473</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>48.225</t>
+          <t>48225047.700033</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>47.065</t>
+          <t>47064511.6462895</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>30.497</t>
+          <t>30497418.7775271</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>48.839</t>
+          <t>48839396.4109763</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.519</t>
+          <t>48519050.9639756</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>51529577.7032102</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.73</t>
+          <t>60730427.1835034</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>63.681</t>
+          <t>63681478.4881332</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>89.299</t>
+          <t>89298976.2900018</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>97.19</t>
+          <t>97190330.1800579</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>88.065</t>
+          <t>88065482.8034427</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>92.003</t>
+          <t>92003360.8795155</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85599891.1557308</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>88.999</t>
+          <t>88998591.263628</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>87.516</t>
+          <t>87515912.7268944</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>66.505</t>
+          <t>66504564.0742462</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>69.693</t>
+          <t>69692993.8653576</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>54.936</t>
+          <t>54936459.3604558</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>68.525</t>
+          <t>68525008.9577904</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>67.339</t>
+          <t>67338843.8414265</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>39.984</t>
+          <t>39984205.3563775</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>35.878</t>
+          <t>35877713.3695642</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>43.375</t>
+          <t>43375422.1554009</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>48.177</t>
+          <t>48176893.3250257</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>53.867</t>
+          <t>53867132.5549622</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>47.289</t>
+          <t>47288840.7912922</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>44.569</t>
+          <t>44568583.1586336</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>36.999</t>
+          <t>36999287.8502964</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>41.017</t>
+          <t>41017470.6138095</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>36.911</t>
+          <t>36911314.6334666</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>33.149</t>
+          <t>33149086.410879</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>24.395</t>
+          <t>24395388.7591808</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>17.962</t>
+          <t>17961687.4021645</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18.082</t>
+          <t>18082013.467556</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13.861</t>
+          <t>13860531.3792213</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.067</t>
+          <t>12066708.5265558</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14.224</t>
+          <t>14223993.0432986</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>17.166</t>
+          <t>17166153.2597903</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>24.336</t>
+          <t>24336201.1984143</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>23.224</t>
+          <t>23223738.7405842</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18.876</t>
+          <t>18876301.4503446</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19.719</t>
+          <t>19718986.7004708</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>17990202.6696558</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>20.029</t>
+          <t>20028881.5404034</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>18.366</t>
+          <t>18366225.3763597</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>13970152.3968123</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>10.513</t>
+          <t>10513188.3486126</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>12.411</t>
+          <t>12411413.2662994</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>43.408</t>
+          <t>43407791.7562675</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>41.706</t>
+          <t>41705641.6384792</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.277</t>
+          <t>28277330.8559204</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>36.876</t>
+          <t>36876006.7485429</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>51.537</t>
+          <t>51537484.631733</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>57.081</t>
+          <t>57081496.1446112</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>58.258</t>
+          <t>58258424.18037</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>62.761</t>
+          <t>62760707.5866485</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>57.057</t>
+          <t>57057131.5043524</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>75.373</t>
+          <t>75373162.3544649</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>316.115</t>
+          <t>316115167.846724</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>80820274.9266166</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>37.026</t>
+          <t>37026067.4494974</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>22.532</t>
+          <t>22531906.320953</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>19.436</t>
+          <t>19436067.4357291</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>28.511</t>
+          <t>28510800.7148522</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25.938</t>
+          <t>25938156.1524634</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.579</t>
+          <t>20579129.0604695</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23.427</t>
+          <t>23426503.5007523</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>26.797</t>
+          <t>26797450.07407</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>31.372</t>
+          <t>31371903.6834419</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>35.568</t>
+          <t>35567870.431994</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>34.578</t>
+          <t>34577896.9614808</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>34.769</t>
+          <t>34769380.775039</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>34.044</t>
+          <t>34043554.1026481</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>33.592</t>
+          <t>33592354.703718</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>30.061</t>
+          <t>30061054.4890202</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>23.786</t>
+          <t>23785518.4582819</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21729665.0509093</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>19.537</t>
+          <t>19537209.4295532</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>49.761</t>
+          <t>49760852.5583581</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>54380380.6848098</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.274</t>
+          <t>37274166.6265925</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.343</t>
+          <t>41342600.2944344</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>61.386</t>
+          <t>61386148.6257488</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>80.584</t>
+          <t>80584195.0080519</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>69.886</t>
+          <t>69885653.1207879</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>68120444.5595706</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>62.043</t>
+          <t>62042522.2725739</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>53.682</t>
+          <t>53682419.8206142</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>63.757</t>
+          <t>63756549.185154</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>60.744</t>
+          <t>60744279.382343</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>45980126.1618075</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>41.334</t>
+          <t>41333680.3436771</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>33.695</t>
+          <t>33695335.5192469</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>29.467</t>
+          <t>29466654.1050434</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>28.199</t>
+          <t>28198513.1864685</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.798</t>
+          <t>23797905.3876094</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28.164</t>
+          <t>28163894.0150025</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>36.939</t>
+          <t>36939178.1902509</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>48.391</t>
+          <t>48390873.1039449</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>47.064</t>
+          <t>47064342.281933</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>39.837</t>
+          <t>39837245.9193404</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>36679891.7935003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34699728.0182059</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>41.166</t>
+          <t>41165916.2194371</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>40.619</t>
+          <t>40619048.3722659</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>29.044</t>
+          <t>29043755.0183722</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>25.089</t>
+          <t>25089089.5201115</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>19.762</t>
+          <t>19762175.1068365</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21.669</t>
+          <t>21669427.112541</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.598</t>
+          <t>21598000.3828793</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16.631</t>
+          <t>16631066.7639908</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>19.359</t>
+          <t>19359063.5561001</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24.542</t>
+          <t>24542238.7271212</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>36.392</t>
+          <t>36392217.4941152</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>36.383</t>
+          <t>36383113.7418559</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>36.421</t>
+          <t>36421406.495761</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>35.133</t>
+          <t>35133054.2003624</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30.466</t>
+          <t>30465572.8196222</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>32.251</t>
+          <t>32250864.0817971</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>30.528</t>
+          <t>30527720.9033847</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>23.632</t>
+          <t>23631853.9101488</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>16.921</t>
+          <t>16920882.2112838</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>13.238</t>
+          <t>13237721.2312409</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>29.985</t>
+          <t>29984788.8011487</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>27.965</t>
+          <t>27965038.2989377</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>24.137</t>
+          <t>24136711.2507172</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24.069</t>
+          <t>24068727.7832768</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>33.574</t>
+          <t>33574155.7360763</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>58.801</t>
+          <t>58801394.2085359</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>58.652</t>
+          <t>58651711.8540222</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>52120497.5081987</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>48.055</t>
+          <t>48055386.0121108</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>47.885</t>
+          <t>47884960.855359</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>58.673</t>
+          <t>58672800.1275803</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>52.205</t>
+          <t>52205425.11352</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>40.094</t>
+          <t>40094233.6459604</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>39.212</t>
+          <t>39212266.4374168</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>24.233</t>
+          <t>24233098.1877145</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>73.894</t>
+          <t>73893543.2673599</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>65.237</t>
+          <t>65236525.9269551</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>61.126</t>
+          <t>61126160.2688867</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>54.516</t>
+          <t>54515610.7726179</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>66.478</t>
+          <t>66478037.8449736</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>82.335</t>
+          <t>82334637.3640772</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>94.235</t>
+          <t>94235096.2932113</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>84.117</t>
+          <t>84117416.6482771</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>68.287</t>
+          <t>68286537.5182981</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>64.918</t>
+          <t>64918418.7043454</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>56.437</t>
+          <t>56436767.6976613</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>54859946.1376471</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>26.554</t>
+          <t>26554044.3929245</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>25.256</t>
+          <t>25255604.2018167</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>20.395</t>
+          <t>20394967.7580177</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>62.324</t>
+          <t>62323554.6306449</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>46.899</t>
+          <t>46898865.4089021</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>36.476</t>
+          <t>36475849.9861524</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>47.333</t>
+          <t>47333476.9411665</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>68.007</t>
+          <t>68006929.2469918</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>72.381</t>
+          <t>72381000.7943434</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>63.351</t>
+          <t>63351440.5461924</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>53.716</t>
+          <t>53716310.9357589</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>48.697</t>
+          <t>48696950.071105</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>39.035</t>
+          <t>39035423.6466275</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>36.301</t>
+          <t>36301337.8771693</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>27.567</t>
+          <t>27567040.8948416</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>20.068</t>
+          <t>20067746.7460582</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>15.855</t>
+          <t>15855449.5736643</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>15.429</t>
+          <t>15428878.326028</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>23.683</t>
+          <t>23682504.8618969</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22.845</t>
+          <t>22844596.0401269</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18.545</t>
+          <t>18545415.9716833</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21.831</t>
+          <t>21831085.7389921</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>27.759</t>
+          <t>27758553.0589814</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>34.862</t>
+          <t>34862075.9531494</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>41.404</t>
+          <t>41404111.6571979</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>34.957</t>
+          <t>34956624.8317968</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>32.682</t>
+          <t>32682006.5850252</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>45.031</t>
+          <t>45031459.8917031</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>46.721</t>
+          <t>46720931.9708579</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>43.002</t>
+          <t>43001791.0512095</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>31.064</t>
+          <t>31063546.3971509</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>22.574</t>
+          <t>22573546.8057331</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>22.431</t>
+          <t>22431219.0008326</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>28.587</t>
+          <t>28586969.2207996</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>29.643</t>
+          <t>29643286.7271708</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>23.165</t>
+          <t>23165366.3782494</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>24.219</t>
+          <t>24218880.3699857</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>33.042</t>
+          <t>33042278.5388042</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>47.166</t>
+          <t>47165976.5452869</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>48.576</t>
+          <t>48575611.8730815</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>45.831</t>
+          <t>45831406.8666545</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>44.551</t>
+          <t>44551033.3255894</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>38.304</t>
+          <t>38304279.9244791</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>42.666</t>
+          <t>42666308.3929907</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>40.267</t>
+          <t>40267088.4429648</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>29.234</t>
+          <t>29233564.3693393</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>31.474</t>
+          <t>31473781.3862318</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>22.564</t>
+          <t>22564004.3745403</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28.683</t>
+          <t>28682653.838833</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>23.506</t>
+          <t>23505949.5548584</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.671</t>
+          <t>20671046.7491702</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>22.691</t>
+          <t>22691154.3466167</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>30.592</t>
+          <t>30591760.9719607</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>43990216.5746978</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>48.599</t>
+          <t>48598940.8227441</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>38.267</t>
+          <t>38266757.3191992</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>37.799</t>
+          <t>37799077.2527709</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>30.463</t>
+          <t>30463424.0419606</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>31.975</t>
+          <t>31974966.1605799</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>31.026</t>
+          <t>31026187.0296391</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>22.404</t>
+          <t>22404357.2146833</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>16.988</t>
+          <t>16988442.1503384</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>13.841</t>
+          <t>13841355.9654496</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>34.648</t>
+          <t>34648115.3173027</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>35.746</t>
+          <t>35746181.3810827</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>38.513</t>
+          <t>38512943.8067546</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>39.539</t>
+          <t>39539250.583694</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>44.998</t>
+          <t>44998144.4673374</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>82.51</t>
+          <t>82509550.2572551</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>109.897</t>
+          <t>109897246.351773</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>144.313</t>
+          <t>144313269.575062</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>131.684</t>
+          <t>131684169.066338</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>110.002</t>
+          <t>110002056.782061</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>108.254</t>
+          <t>108254168.171854</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>108.907</t>
+          <t>108906598.762923</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>75.505</t>
+          <t>75505137.1310516</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>47.205</t>
+          <t>47205182.114463</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>47.806</t>
+          <t>47805871.629096</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>51.827</t>
+          <t>51827196.6287729</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>47.096</t>
+          <t>47095599.1847612</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>42.395</t>
+          <t>42394914.3907843</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>51.915</t>
+          <t>51914717.1810359</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>63.172</t>
+          <t>63171531.2047528</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>89.431</t>
+          <t>89431389.0201876</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>98.819</t>
+          <t>98818511.002553</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>109.892</t>
+          <t>109891974.220968</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>112.545</t>
+          <t>112545085.284224</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>107.26</t>
+          <t>107260351.233288</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>107.252</t>
+          <t>107252167.715845</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>106.863</t>
+          <t>106863380.120653</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>83.008</t>
+          <t>83007952.9170775</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>78.802</t>
+          <t>78801735.4901071</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>55.271</t>
+          <t>55271181.743487</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>23.158</t>
+          <t>23158389.1570257</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21.546</t>
+          <t>21546119.5617444</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.424</t>
+          <t>19424443.8523769</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>19.092</t>
+          <t>19091934.0999074</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>25.226</t>
+          <t>25225881.0385523</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>38.003</t>
+          <t>38002922.6563076</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>36.502</t>
+          <t>36501703.003282</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>34.975</t>
+          <t>34975413.7698382</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>35.018</t>
+          <t>35017828.9585204</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>35.417</t>
+          <t>35417461.5262528</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>39.414</t>
+          <t>39414497.9417753</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>36.465</t>
+          <t>36464989.7463002</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>28.742</t>
+          <t>28742125.8533467</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>27169776.0203501</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17129831.2898475</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>564.07</t>
+          <t>564070080.79715</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>513.271</t>
+          <t>513271377.952137</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>539.746</t>
+          <t>539745616.065954</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>589.544</t>
+          <t>589543588.116689</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>631.318</t>
+          <t>631317905.249044</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>730.389</t>
+          <t>730388796.642105</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>768.207</t>
+          <t>768207453.689062</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>748.327</t>
+          <t>748326674.024044</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>701.932</t>
+          <t>701931594.723171</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>580.788</t>
+          <t>580788422.998457</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>519.043</t>
+          <t>519042880.749168</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>443.654</t>
+          <t>443654167.812444</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>325.472</t>
+          <t>325471743.016466</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>250.917</t>
+          <t>250917011.227365</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>245.788</t>
+          <t>245788086.52007</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2249.557</t>
+          <t>2249556525.49449</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2089.66</t>
+          <t>2089660356.53602</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1898.915</t>
+          <t>1898914780.79106</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2069.064</t>
+          <t>2069064342.22669</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2348.529</t>
+          <t>2348528999.73894</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3120.938</t>
+          <t>3120937907.2513</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3370.743</t>
+          <t>3370743333.30277</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3232.942</t>
+          <t>3232942352.1711</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3056.451</t>
+          <t>3056451036.61884</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2758.403</t>
+          <t>2758402879.16823</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2947.199</t>
+          <t>2947199182.20509</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2524.315</t>
+          <t>2524315072.67621</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1863.97</t>
+          <t>1863970480.29297</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1578.043</t>
+          <t>1578042649.8252</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1292.504</t>
+          <t>1292504324.66492</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
